--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>132124646</v>
       </c>
       <c r="B10" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>132124654</v>
       </c>
       <c r="B11" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>132124649</v>
       </c>
       <c r="B12" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>132125217</v>
       </c>
       <c r="B13" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124629</v>
+        <v>132124642</v>
       </c>
       <c r="B17" t="n">
-        <v>4781</v>
+        <v>101304</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655110</v>
+        <v>655151</v>
       </c>
       <c r="R17" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,12 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,10 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124642</v>
+        <v>132124629</v>
       </c>
       <c r="B18" t="n">
-        <v>101301</v>
+        <v>4781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2446,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2475,13 +2470,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655151</v>
+        <v>655110</v>
       </c>
       <c r="R18" t="n">
-        <v>6647732</v>
+        <v>6647839</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,7 +2505,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2515,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,57 +2547,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132124658</v>
+        <v>132124632</v>
       </c>
       <c r="B19" t="n">
-        <v>99095</v>
+        <v>5199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655194</v>
+        <v>655113</v>
       </c>
       <c r="R19" t="n">
-        <v>6647705</v>
+        <v>6647802</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,7 +2617,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2627,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,48 +2654,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132124632</v>
+        <v>132124658</v>
       </c>
       <c r="B20" t="n">
-        <v>5199</v>
+        <v>99098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655113</v>
+        <v>655194</v>
       </c>
       <c r="R20" t="n">
-        <v>6647802</v>
+        <v>6647705</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,7 +2773,7 @@
         <v>132124651</v>
       </c>
       <c r="B21" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>132124668</v>
       </c>
       <c r="B23" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>132124624</v>
       </c>
       <c r="B24" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>132124667</v>
       </c>
       <c r="B26" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>132124663</v>
       </c>
       <c r="B29" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>132124622</v>
       </c>
       <c r="B30" t="n">
-        <v>92612</v>
+        <v>92615</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>132124661</v>
       </c>
       <c r="B31" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -2547,48 +2547,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132124632</v>
+        <v>132124658</v>
       </c>
       <c r="B19" t="n">
-        <v>5199</v>
+        <v>99098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655113</v>
+        <v>655194</v>
       </c>
       <c r="R19" t="n">
-        <v>6647802</v>
+        <v>6647705</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2627,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,57 +2663,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132124658</v>
+        <v>132124632</v>
       </c>
       <c r="B20" t="n">
-        <v>99098</v>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655194</v>
+        <v>655113</v>
       </c>
       <c r="R20" t="n">
-        <v>6647705</v>
+        <v>6647802</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -2547,57 +2547,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132124658</v>
+        <v>132124632</v>
       </c>
       <c r="B19" t="n">
-        <v>99098</v>
+        <v>5199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655194</v>
+        <v>655113</v>
       </c>
       <c r="R19" t="n">
-        <v>6647705</v>
+        <v>6647802</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,7 +2617,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2627,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,48 +2654,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132124632</v>
+        <v>132124658</v>
       </c>
       <c r="B20" t="n">
-        <v>5199</v>
+        <v>99098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655113</v>
+        <v>655194</v>
       </c>
       <c r="R20" t="n">
-        <v>6647802</v>
+        <v>6647705</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3871,57 +3871,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132124661</v>
+        <v>132124631</v>
       </c>
       <c r="B31" t="n">
-        <v>99098</v>
+        <v>4781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655238</v>
+        <v>655117</v>
       </c>
       <c r="R31" t="n">
-        <v>6647732</v>
+        <v>6647809</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3950,7 +3941,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,7 +3951,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3987,48 +3983,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132124631</v>
+        <v>132124661</v>
       </c>
       <c r="B32" t="n">
-        <v>4781</v>
+        <v>99098</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655117</v>
+        <v>655238</v>
       </c>
       <c r="R32" t="n">
-        <v>6647809</v>
+        <v>6647732</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4057,7 +4062,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4067,12 +4072,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -1883,60 +1883,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132125217</v>
+        <v>132124656</v>
       </c>
       <c r="B13" t="n">
-        <v>58109</v>
+        <v>4781</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655073</v>
+        <v>655254</v>
       </c>
       <c r="R13" t="n">
-        <v>6647799</v>
+        <v>6647688</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1965,7 +1953,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1963,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,48 +1990,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132124656</v>
+        <v>132125217</v>
       </c>
       <c r="B14" t="n">
-        <v>4781</v>
+        <v>58109</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655254</v>
+        <v>655073</v>
       </c>
       <c r="R14" t="n">
-        <v>6647688</v>
+        <v>6647799</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2072,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2082,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,32 +2114,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132124670</v>
+        <v>132124633</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655140</v>
+        <v>655113</v>
       </c>
       <c r="R15" t="n">
-        <v>6647863</v>
+        <v>6647802</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,32 +2221,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132124633</v>
+        <v>132124670</v>
       </c>
       <c r="B16" t="n">
-        <v>5179</v>
+        <v>57945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655113</v>
+        <v>655140</v>
       </c>
       <c r="R16" t="n">
-        <v>6647802</v>
+        <v>6647863</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124642</v>
+        <v>132124629</v>
       </c>
       <c r="B17" t="n">
-        <v>101304</v>
+        <v>4781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655151</v>
+        <v>655110</v>
       </c>
       <c r="R17" t="n">
-        <v>6647732</v>
+        <v>6647839</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2408,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,10 +2440,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124629</v>
+        <v>132124642</v>
       </c>
       <c r="B18" t="n">
-        <v>4781</v>
+        <v>101304</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2470,13 +2475,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655110</v>
+        <v>655151</v>
       </c>
       <c r="R18" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2505,7 +2510,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2515,12 +2520,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124629</v>
+        <v>132124642</v>
       </c>
       <c r="B17" t="n">
-        <v>4781</v>
+        <v>101304</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655110</v>
+        <v>655151</v>
       </c>
       <c r="R17" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,12 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,10 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124642</v>
+        <v>132124629</v>
       </c>
       <c r="B18" t="n">
-        <v>101304</v>
+        <v>4781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2446,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2475,13 +2470,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655151</v>
+        <v>655110</v>
       </c>
       <c r="R18" t="n">
-        <v>6647732</v>
+        <v>6647839</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,7 +2505,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2515,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3871,48 +3871,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132124631</v>
+        <v>132124661</v>
       </c>
       <c r="B31" t="n">
-        <v>4781</v>
+        <v>99098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655117</v>
+        <v>655238</v>
       </c>
       <c r="R31" t="n">
-        <v>6647809</v>
+        <v>6647732</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3941,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3951,12 +3960,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,57 +3987,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132124661</v>
+        <v>132124631</v>
       </c>
       <c r="B32" t="n">
-        <v>99098</v>
+        <v>4781</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655238</v>
+        <v>655117</v>
       </c>
       <c r="R32" t="n">
-        <v>6647732</v>
+        <v>6647809</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4062,7 +4057,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4072,7 +4067,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124642</v>
+        <v>132124629</v>
       </c>
       <c r="B17" t="n">
-        <v>101304</v>
+        <v>4781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655151</v>
+        <v>655110</v>
       </c>
       <c r="R17" t="n">
-        <v>6647732</v>
+        <v>6647839</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2408,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,10 +2440,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124629</v>
+        <v>132124642</v>
       </c>
       <c r="B18" t="n">
-        <v>4781</v>
+        <v>101304</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2470,13 +2475,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655110</v>
+        <v>655151</v>
       </c>
       <c r="R18" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2505,7 +2510,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2515,12 +2520,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3871,57 +3871,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132124661</v>
+        <v>132124631</v>
       </c>
       <c r="B31" t="n">
-        <v>99098</v>
+        <v>4781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655238</v>
+        <v>655117</v>
       </c>
       <c r="R31" t="n">
-        <v>6647732</v>
+        <v>6647809</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3950,7 +3941,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,7 +3951,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3987,48 +3983,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132124631</v>
+        <v>132124661</v>
       </c>
       <c r="B32" t="n">
-        <v>4781</v>
+        <v>99098</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655117</v>
+        <v>655238</v>
       </c>
       <c r="R32" t="n">
-        <v>6647809</v>
+        <v>6647732</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4057,7 +4062,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4067,12 +4072,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -3871,48 +3871,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132124631</v>
+        <v>132124661</v>
       </c>
       <c r="B31" t="n">
-        <v>4781</v>
+        <v>99098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655117</v>
+        <v>655238</v>
       </c>
       <c r="R31" t="n">
-        <v>6647809</v>
+        <v>6647732</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3941,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3951,12 +3960,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,57 +3987,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132124661</v>
+        <v>132124631</v>
       </c>
       <c r="B32" t="n">
-        <v>99098</v>
+        <v>4781</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655238</v>
+        <v>655117</v>
       </c>
       <c r="R32" t="n">
-        <v>6647732</v>
+        <v>6647809</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4062,7 +4057,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4072,7 +4067,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>132124646</v>
       </c>
       <c r="B10" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>132124654</v>
       </c>
       <c r="B11" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>132124649</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>132125217</v>
       </c>
       <c r="B14" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>132124670</v>
       </c>
       <c r="B16" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124629</v>
+        <v>132124642</v>
       </c>
       <c r="B17" t="n">
-        <v>4781</v>
+        <v>101312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655110</v>
+        <v>655151</v>
       </c>
       <c r="R17" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,12 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,10 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124642</v>
+        <v>132124629</v>
       </c>
       <c r="B18" t="n">
-        <v>101304</v>
+        <v>4781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2446,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2475,13 +2470,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655151</v>
+        <v>655110</v>
       </c>
       <c r="R18" t="n">
-        <v>6647732</v>
+        <v>6647839</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,7 +2505,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2515,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2657,7 +2657,7 @@
         <v>132124658</v>
       </c>
       <c r="B20" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>132124651</v>
       </c>
       <c r="B21" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>132124668</v>
       </c>
       <c r="B23" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>132124624</v>
       </c>
       <c r="B24" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>132124623</v>
       </c>
       <c r="B25" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>132124667</v>
       </c>
       <c r="B26" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>132124663</v>
       </c>
       <c r="B29" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>132124622</v>
       </c>
       <c r="B30" t="n">
-        <v>92615</v>
+        <v>92621</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3871,57 +3871,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132124661</v>
+        <v>132124631</v>
       </c>
       <c r="B31" t="n">
-        <v>99098</v>
+        <v>4781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655238</v>
+        <v>655117</v>
       </c>
       <c r="R31" t="n">
-        <v>6647732</v>
+        <v>6647809</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3950,7 +3941,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,7 +3951,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3987,48 +3983,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132124631</v>
+        <v>132124661</v>
       </c>
       <c r="B32" t="n">
-        <v>4781</v>
+        <v>99106</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655117</v>
+        <v>655238</v>
       </c>
       <c r="R32" t="n">
-        <v>6647809</v>
+        <v>6647732</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4057,7 +4062,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4067,12 +4072,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -3871,48 +3871,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132124631</v>
+        <v>132124661</v>
       </c>
       <c r="B31" t="n">
-        <v>4781</v>
+        <v>99106</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655117</v>
+        <v>655238</v>
       </c>
       <c r="R31" t="n">
-        <v>6647809</v>
+        <v>6647732</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3941,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3951,12 +3960,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,57 +3987,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132124661</v>
+        <v>132124631</v>
       </c>
       <c r="B32" t="n">
-        <v>99106</v>
+        <v>4781</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655238</v>
+        <v>655117</v>
       </c>
       <c r="R32" t="n">
-        <v>6647732</v>
+        <v>6647809</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4062,7 +4057,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4072,7 +4067,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>132124646</v>
       </c>
       <c r="B10" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>132124654</v>
       </c>
       <c r="B11" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>132124649</v>
       </c>
       <c r="B12" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>132125217</v>
       </c>
       <c r="B14" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>132124670</v>
       </c>
       <c r="B16" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>132124642</v>
       </c>
       <c r="B17" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2547,48 +2547,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132124632</v>
+        <v>132124658</v>
       </c>
       <c r="B19" t="n">
-        <v>5199</v>
+        <v>99116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655113</v>
+        <v>655194</v>
       </c>
       <c r="R19" t="n">
-        <v>6647802</v>
+        <v>6647705</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2627,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,57 +2663,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132124658</v>
+        <v>132124632</v>
       </c>
       <c r="B20" t="n">
-        <v>99106</v>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655194</v>
+        <v>655113</v>
       </c>
       <c r="R20" t="n">
-        <v>6647705</v>
+        <v>6647802</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,7 +2773,7 @@
         <v>132124651</v>
       </c>
       <c r="B21" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>132124668</v>
       </c>
       <c r="B23" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>132124624</v>
       </c>
       <c r="B24" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>132124623</v>
       </c>
       <c r="B25" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>132124667</v>
       </c>
       <c r="B26" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>132124663</v>
       </c>
       <c r="B29" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>132124622</v>
       </c>
       <c r="B30" t="n">
-        <v>92621</v>
+        <v>92631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3871,57 +3871,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132124661</v>
+        <v>132124631</v>
       </c>
       <c r="B31" t="n">
-        <v>99106</v>
+        <v>4781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655238</v>
+        <v>655117</v>
       </c>
       <c r="R31" t="n">
-        <v>6647732</v>
+        <v>6647809</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3950,7 +3941,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,7 +3951,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3987,48 +3983,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132124631</v>
+        <v>132124661</v>
       </c>
       <c r="B32" t="n">
-        <v>4781</v>
+        <v>99116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655117</v>
+        <v>655238</v>
       </c>
       <c r="R32" t="n">
-        <v>6647809</v>
+        <v>6647732</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4057,7 +4062,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4067,12 +4072,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -1660,48 +1660,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132124654</v>
+        <v>132124649</v>
       </c>
       <c r="B11" t="n">
-        <v>91908</v>
+        <v>99116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655254</v>
+        <v>655171</v>
       </c>
       <c r="R11" t="n">
-        <v>6647727</v>
+        <v>6647768</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,7 +1739,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1749,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,57 +1776,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132124649</v>
+        <v>132124654</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>91908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655171</v>
+        <v>655254</v>
       </c>
       <c r="R12" t="n">
-        <v>6647768</v>
+        <v>6647727</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124642</v>
+        <v>132124629</v>
       </c>
       <c r="B17" t="n">
-        <v>101323</v>
+        <v>4781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655151</v>
+        <v>655110</v>
       </c>
       <c r="R17" t="n">
-        <v>6647732</v>
+        <v>6647839</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2408,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,10 +2440,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124629</v>
+        <v>132124642</v>
       </c>
       <c r="B18" t="n">
-        <v>4781</v>
+        <v>101323</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2470,13 +2475,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655110</v>
+        <v>655151</v>
       </c>
       <c r="R18" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2505,7 +2510,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2515,12 +2520,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>132124646</v>
       </c>
       <c r="B10" t="n">
-        <v>101323</v>
+        <v>101325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,57 +1660,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132124649</v>
+        <v>132124654</v>
       </c>
       <c r="B11" t="n">
-        <v>99116</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655171</v>
+        <v>655254</v>
       </c>
       <c r="R11" t="n">
-        <v>6647768</v>
+        <v>6647727</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1739,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1749,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,48 +1767,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132124654</v>
+        <v>132124649</v>
       </c>
       <c r="B12" t="n">
-        <v>91908</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655254</v>
+        <v>655171</v>
       </c>
       <c r="R12" t="n">
-        <v>6647727</v>
+        <v>6647768</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2114,32 +2114,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132124633</v>
+        <v>132124670</v>
       </c>
       <c r="B15" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655113</v>
+        <v>655140</v>
       </c>
       <c r="R15" t="n">
-        <v>6647802</v>
+        <v>6647863</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,32 +2221,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132124670</v>
+        <v>132124633</v>
       </c>
       <c r="B16" t="n">
-        <v>57950</v>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655140</v>
+        <v>655113</v>
       </c>
       <c r="R16" t="n">
-        <v>6647863</v>
+        <v>6647802</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,7 +2443,7 @@
         <v>132124642</v>
       </c>
       <c r="B18" t="n">
-        <v>101323</v>
+        <v>101325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,57 +2547,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132124658</v>
+        <v>132124632</v>
       </c>
       <c r="B19" t="n">
-        <v>99116</v>
+        <v>5199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655194</v>
+        <v>655113</v>
       </c>
       <c r="R19" t="n">
-        <v>6647705</v>
+        <v>6647802</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,7 +2617,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2627,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,48 +2654,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132124632</v>
+        <v>132124658</v>
       </c>
       <c r="B20" t="n">
-        <v>5199</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655113</v>
+        <v>655194</v>
       </c>
       <c r="R20" t="n">
-        <v>6647802</v>
+        <v>6647705</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,7 +2773,7 @@
         <v>132124651</v>
       </c>
       <c r="B21" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>132124624</v>
       </c>
       <c r="B24" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>132124667</v>
       </c>
       <c r="B26" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>132124663</v>
       </c>
       <c r="B29" t="n">
-        <v>101323</v>
+        <v>101325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>132124622</v>
       </c>
       <c r="B30" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>132124661</v>
       </c>
       <c r="B32" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>132124646</v>
       </c>
       <c r="B10" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,48 +1660,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132124654</v>
+        <v>132124649</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655254</v>
+        <v>655171</v>
       </c>
       <c r="R11" t="n">
-        <v>6647727</v>
+        <v>6647768</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1730,7 +1739,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1749,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,57 +1776,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132124649</v>
+        <v>132124654</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655171</v>
+        <v>655254</v>
       </c>
       <c r="R12" t="n">
-        <v>6647768</v>
+        <v>6647727</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,48 +1883,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132124656</v>
+        <v>132125217</v>
       </c>
       <c r="B13" t="n">
-        <v>4781</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655254</v>
+        <v>655073</v>
       </c>
       <c r="R13" t="n">
-        <v>6647688</v>
+        <v>6647799</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1953,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1963,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,60 +2007,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132125217</v>
+        <v>132124656</v>
       </c>
       <c r="B14" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655073</v>
+        <v>655254</v>
       </c>
       <c r="R14" t="n">
-        <v>6647799</v>
+        <v>6647688</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,12 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124629</v>
+        <v>132124642</v>
       </c>
       <c r="B17" t="n">
-        <v>4781</v>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655110</v>
+        <v>655151</v>
       </c>
       <c r="R17" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,12 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,10 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124642</v>
+        <v>132124629</v>
       </c>
       <c r="B18" t="n">
-        <v>101325</v>
+        <v>4781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2446,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2475,13 +2470,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655151</v>
+        <v>655110</v>
       </c>
       <c r="R18" t="n">
-        <v>6647732</v>
+        <v>6647839</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,7 +2505,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2515,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3660,7 +3660,7 @@
         <v>132124663</v>
       </c>
       <c r="B29" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3871,48 +3871,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132124631</v>
+        <v>132124661</v>
       </c>
       <c r="B31" t="n">
-        <v>4781</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655117</v>
+        <v>655238</v>
       </c>
       <c r="R31" t="n">
-        <v>6647809</v>
+        <v>6647732</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3941,7 +3950,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3951,12 +3960,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3983,57 +3987,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132124661</v>
+        <v>132124631</v>
       </c>
       <c r="B32" t="n">
-        <v>99118</v>
+        <v>4781</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655238</v>
+        <v>655117</v>
       </c>
       <c r="R32" t="n">
-        <v>6647732</v>
+        <v>6647809</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4062,7 +4057,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4072,7 +4067,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -1883,60 +1883,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132125217</v>
+        <v>132124656</v>
       </c>
       <c r="B13" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655073</v>
+        <v>655254</v>
       </c>
       <c r="R13" t="n">
-        <v>6647799</v>
+        <v>6647688</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1965,7 +1953,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1963,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,48 +1990,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132124656</v>
+        <v>132125217</v>
       </c>
       <c r="B14" t="n">
-        <v>4781</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655254</v>
+        <v>655073</v>
       </c>
       <c r="R14" t="n">
-        <v>6647688</v>
+        <v>6647799</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2072,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2082,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>132124646</v>
       </c>
       <c r="B10" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,57 +1660,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132124649</v>
+        <v>132124654</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>91910</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655171</v>
+        <v>655254</v>
       </c>
       <c r="R11" t="n">
-        <v>6647768</v>
+        <v>6647727</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1739,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1749,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,48 +1767,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132124654</v>
+        <v>132124649</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>99119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655254</v>
+        <v>655171</v>
       </c>
       <c r="R12" t="n">
-        <v>6647727</v>
+        <v>6647768</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,48 +1883,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132124656</v>
+        <v>132125217</v>
       </c>
       <c r="B13" t="n">
-        <v>4781</v>
+        <v>58115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655254</v>
+        <v>655073</v>
       </c>
       <c r="R13" t="n">
-        <v>6647688</v>
+        <v>6647799</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1953,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1963,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,60 +2007,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132125217</v>
+        <v>132124656</v>
       </c>
       <c r="B14" t="n">
-        <v>58114</v>
+        <v>4781</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655073</v>
+        <v>655254</v>
       </c>
       <c r="R14" t="n">
-        <v>6647799</v>
+        <v>6647688</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,12 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2117,7 +2117,7 @@
         <v>132124670</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124642</v>
+        <v>132124629</v>
       </c>
       <c r="B17" t="n">
-        <v>101326</v>
+        <v>4781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655151</v>
+        <v>655110</v>
       </c>
       <c r="R17" t="n">
-        <v>6647732</v>
+        <v>6647839</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2408,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,10 +2440,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124629</v>
+        <v>132124642</v>
       </c>
       <c r="B18" t="n">
-        <v>4781</v>
+        <v>101327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2470,13 +2475,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655110</v>
+        <v>655151</v>
       </c>
       <c r="R18" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2505,7 +2510,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2515,12 +2520,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,48 +2547,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132124632</v>
+        <v>132124658</v>
       </c>
       <c r="B19" t="n">
-        <v>5199</v>
+        <v>99119</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655113</v>
+        <v>655194</v>
       </c>
       <c r="R19" t="n">
-        <v>6647802</v>
+        <v>6647705</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2627,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,57 +2663,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132124658</v>
+        <v>132124632</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655194</v>
+        <v>655113</v>
       </c>
       <c r="R20" t="n">
-        <v>6647705</v>
+        <v>6647802</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,7 +2773,7 @@
         <v>132124651</v>
       </c>
       <c r="B21" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>132124668</v>
       </c>
       <c r="B23" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>132124624</v>
       </c>
       <c r="B24" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>132124623</v>
       </c>
       <c r="B25" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>132124667</v>
       </c>
       <c r="B26" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>132124663</v>
       </c>
       <c r="B29" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>132124622</v>
       </c>
       <c r="B30" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3871,57 +3871,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132124661</v>
+        <v>132124631</v>
       </c>
       <c r="B31" t="n">
-        <v>99118</v>
+        <v>4781</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655238</v>
+        <v>655117</v>
       </c>
       <c r="R31" t="n">
-        <v>6647732</v>
+        <v>6647809</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3950,7 +3941,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3960,7 +3951,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3987,48 +3983,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132124631</v>
+        <v>132124661</v>
       </c>
       <c r="B32" t="n">
-        <v>4781</v>
+        <v>99119</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655117</v>
+        <v>655238</v>
       </c>
       <c r="R32" t="n">
-        <v>6647809</v>
+        <v>6647732</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4057,7 +4062,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4067,12 +4072,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -1556,7 +1556,7 @@
         <v>132124646</v>
       </c>
       <c r="B10" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>132124654</v>
       </c>
       <c r="B11" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>132124649</v>
       </c>
       <c r="B12" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,60 +1883,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132125217</v>
+        <v>132124656</v>
       </c>
       <c r="B13" t="n">
-        <v>58115</v>
+        <v>4781</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655073</v>
+        <v>655254</v>
       </c>
       <c r="R13" t="n">
-        <v>6647799</v>
+        <v>6647688</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1965,7 +1953,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1963,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,48 +1990,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132124656</v>
+        <v>132125217</v>
       </c>
       <c r="B14" t="n">
-        <v>4781</v>
+        <v>58115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655254</v>
+        <v>655073</v>
       </c>
       <c r="R14" t="n">
-        <v>6647688</v>
+        <v>6647799</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2072,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2082,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124629</v>
+        <v>132124642</v>
       </c>
       <c r="B17" t="n">
-        <v>4781</v>
+        <v>101329</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655110</v>
+        <v>655151</v>
       </c>
       <c r="R17" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,12 +2408,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,10 +2435,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124642</v>
+        <v>132124629</v>
       </c>
       <c r="B18" t="n">
-        <v>101327</v>
+        <v>4781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,21 +2446,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2475,13 +2470,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655151</v>
+        <v>655110</v>
       </c>
       <c r="R18" t="n">
-        <v>6647732</v>
+        <v>6647839</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,7 +2505,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2520,7 +2515,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,57 +2547,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132124658</v>
+        <v>132124632</v>
       </c>
       <c r="B19" t="n">
-        <v>99119</v>
+        <v>5199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655194</v>
+        <v>655113</v>
       </c>
       <c r="R19" t="n">
-        <v>6647705</v>
+        <v>6647802</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,7 +2617,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2636,7 +2627,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,48 +2654,57 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132124632</v>
+        <v>132124658</v>
       </c>
       <c r="B20" t="n">
-        <v>5199</v>
+        <v>99121</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655113</v>
+        <v>655194</v>
       </c>
       <c r="R20" t="n">
-        <v>6647802</v>
+        <v>6647705</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,7 +2773,7 @@
         <v>132124651</v>
       </c>
       <c r="B21" t="n">
-        <v>92370</v>
+        <v>92372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>132124624</v>
       </c>
       <c r="B24" t="n">
-        <v>92370</v>
+        <v>92372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>132124667</v>
       </c>
       <c r="B26" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>132124663</v>
       </c>
       <c r="B29" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>132124622</v>
       </c>
       <c r="B30" t="n">
-        <v>92633</v>
+        <v>92635</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>132124661</v>
       </c>
       <c r="B32" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1556,7 +1556,7 @@
         <v>132124646</v>
       </c>
       <c r="B10" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>132124654</v>
       </c>
       <c r="B11" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>132124649</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,48 +1883,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132124656</v>
+        <v>132125217</v>
       </c>
       <c r="B13" t="n">
-        <v>4781</v>
+        <v>58115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655254</v>
+        <v>655073</v>
       </c>
       <c r="R13" t="n">
-        <v>6647688</v>
+        <v>6647799</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1953,7 +1965,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1963,7 +1975,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1990,60 +2007,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132125217</v>
+        <v>132124656</v>
       </c>
       <c r="B14" t="n">
-        <v>58115</v>
+        <v>4781</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655073</v>
+        <v>655254</v>
       </c>
       <c r="R14" t="n">
-        <v>6647799</v>
+        <v>6647688</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,7 +2077,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,12 +2087,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,32 +2114,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132124670</v>
+        <v>132124633</v>
       </c>
       <c r="B15" t="n">
-        <v>57951</v>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655140</v>
+        <v>655113</v>
       </c>
       <c r="R15" t="n">
-        <v>6647863</v>
+        <v>6647802</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,32 +2221,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132124633</v>
+        <v>132124670</v>
       </c>
       <c r="B16" t="n">
-        <v>5179</v>
+        <v>57951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655113</v>
+        <v>655140</v>
       </c>
       <c r="R16" t="n">
-        <v>6647802</v>
+        <v>6647863</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,10 +2328,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124642</v>
+        <v>132124629</v>
       </c>
       <c r="B17" t="n">
-        <v>101329</v>
+        <v>4781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655151</v>
+        <v>655110</v>
       </c>
       <c r="R17" t="n">
-        <v>6647732</v>
+        <v>6647839</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,7 +2408,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,10 +2440,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124629</v>
+        <v>132124642</v>
       </c>
       <c r="B18" t="n">
-        <v>4781</v>
+        <v>101330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,21 +2451,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2470,13 +2475,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655110</v>
+        <v>655151</v>
       </c>
       <c r="R18" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2505,7 +2510,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2515,12 +2520,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,48 +2547,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132124632</v>
+        <v>132124658</v>
       </c>
       <c r="B19" t="n">
-        <v>5199</v>
+        <v>99122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655113</v>
+        <v>655194</v>
       </c>
       <c r="R19" t="n">
-        <v>6647802</v>
+        <v>6647705</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2617,7 +2626,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2627,7 +2636,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,57 +2663,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132124658</v>
+        <v>132124632</v>
       </c>
       <c r="B20" t="n">
-        <v>99121</v>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655194</v>
+        <v>655113</v>
       </c>
       <c r="R20" t="n">
-        <v>6647705</v>
+        <v>6647802</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,7 +2773,7 @@
         <v>132124651</v>
       </c>
       <c r="B21" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>132124624</v>
       </c>
       <c r="B24" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>132124667</v>
       </c>
       <c r="B26" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>132124663</v>
       </c>
       <c r="B29" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>132124622</v>
       </c>
       <c r="B30" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>132124661</v>
       </c>
       <c r="B32" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4204,6 +4204,1076 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132976049</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>655097</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6647771</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132976047</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101330</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>655153</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6647721</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132976040</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101330</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>655159</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6647736</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132976044</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101330</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>655143</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6647734</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132976043</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>655141</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6647761</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132976038</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101330</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>655167</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6647731</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132976033</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>655131</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6647804</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132976048</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91913</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>655130</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6647775</v>
+      </c>
+      <c r="S41" t="n">
+        <v>6</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132976035</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101330</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>655173</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6647726</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132976030</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>655073</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6647783</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -4527,32 +4527,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132976044</v>
+        <v>132976043</v>
       </c>
       <c r="B37" t="n">
-        <v>101330</v>
+        <v>91913</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655143</v>
+        <v>655141</v>
       </c>
       <c r="R37" t="n">
-        <v>6647734</v>
+        <v>6647761</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4634,32 +4634,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132976043</v>
+        <v>132976044</v>
       </c>
       <c r="B38" t="n">
-        <v>91913</v>
+        <v>101330</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655141</v>
+        <v>655143</v>
       </c>
       <c r="R38" t="n">
-        <v>6647761</v>
+        <v>6647734</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -4527,32 +4527,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132976044</v>
+        <v>132976043</v>
       </c>
       <c r="B37" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655143</v>
+        <v>655141</v>
       </c>
       <c r="R37" t="n">
-        <v>6647734</v>
+        <v>6647761</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4634,32 +4634,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132976043</v>
+        <v>132976044</v>
       </c>
       <c r="B38" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655141</v>
+        <v>655143</v>
       </c>
       <c r="R38" t="n">
-        <v>6647761</v>
+        <v>6647734</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -4741,32 +4741,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132976033</v>
+        <v>132976038</v>
       </c>
       <c r="B39" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655131</v>
+        <v>655167</v>
       </c>
       <c r="R39" t="n">
-        <v>6647804</v>
+        <v>6647731</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4848,32 +4848,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132976038</v>
+        <v>132976033</v>
       </c>
       <c r="B40" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655167</v>
+        <v>655131</v>
       </c>
       <c r="R40" t="n">
-        <v>6647731</v>
+        <v>6647804</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -4527,32 +4527,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132976043</v>
+        <v>132976044</v>
       </c>
       <c r="B37" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655141</v>
+        <v>655143</v>
       </c>
       <c r="R37" t="n">
-        <v>6647761</v>
+        <v>6647734</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4634,32 +4634,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132976044</v>
+        <v>132976043</v>
       </c>
       <c r="B38" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655143</v>
+        <v>655141</v>
       </c>
       <c r="R38" t="n">
-        <v>6647734</v>
+        <v>6647761</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4741,32 +4741,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132976038</v>
+        <v>132976033</v>
       </c>
       <c r="B39" t="n">
-        <v>101338</v>
+        <v>91918</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655167</v>
+        <v>655131</v>
       </c>
       <c r="R39" t="n">
-        <v>6647731</v>
+        <v>6647804</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4848,32 +4848,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132976033</v>
+        <v>132976038</v>
       </c>
       <c r="B40" t="n">
-        <v>91918</v>
+        <v>101338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655131</v>
+        <v>655167</v>
       </c>
       <c r="R40" t="n">
-        <v>6647804</v>
+        <v>6647731</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 14089-2026 artfynd.xlsx
+++ b/artfynd/A 14089-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131451694</v>
+        <v>131447239</v>
       </c>
       <c r="B2" t="n">
-        <v>57911</v>
+        <v>90946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>889</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tomta, Tomta, Upl</t>
+          <t>Stamsäng, Stamsäng, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655117</v>
+        <v>655260</v>
       </c>
       <c r="R2" t="n">
-        <v>6647895</v>
+        <v>6647655</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131449258</v>
+        <v>131451081</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>90946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>889</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tomta, Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655165</v>
+        <v>655019</v>
       </c>
       <c r="R3" t="n">
-        <v>6647775</v>
+        <v>6647832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,11 +892,11 @@
         <v>131449047</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131449391</v>
+        <v>131449258</v>
       </c>
       <c r="B5" t="n">
-        <v>57911</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Tomta, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655145</v>
+        <v>655165</v>
       </c>
       <c r="R5" t="n">
-        <v>6647787</v>
+        <v>6647775</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,54 +1103,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448213</v>
+        <v>131460976</v>
       </c>
       <c r="B6" t="n">
-        <v>99054</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stamsäng, Stamsäng, Upl</t>
+          <t>Stamsäng, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655284</v>
+        <v>655244</v>
       </c>
       <c r="R6" t="n">
-        <v>6647716</v>
+        <v>6647615</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,27 +1174,18 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,48 +1204,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131451614</v>
+        <v>132124654</v>
       </c>
       <c r="B7" t="n">
-        <v>92308</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tomta, Tomta, Upl</t>
+          <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655081</v>
+        <v>655254</v>
       </c>
       <c r="R7" t="n">
-        <v>6647893</v>
+        <v>6647727</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,22 +1269,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131447239</v>
+        <v>132124667</v>
       </c>
       <c r="B8" t="n">
-        <v>90885</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,37 +1322,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>889</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stamsäng, Stamsäng, Upl</t>
+          <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655260</v>
+        <v>655176</v>
       </c>
       <c r="R8" t="n">
-        <v>6647655</v>
+        <v>6647822</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,22 +1376,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,60 +1418,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131448147</v>
+        <v>132976033</v>
       </c>
       <c r="B9" t="n">
-        <v>99054</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stamsäng, Stamsäng, Upl</t>
+          <t>Kashimirhagen SV, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655291</v>
+        <v>655131</v>
       </c>
       <c r="R9" t="n">
-        <v>6647717</v>
+        <v>6647804</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1510,22 +1483,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1507,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1553,48 +1525,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132124646</v>
+        <v>132976043</v>
       </c>
       <c r="B10" t="n">
-        <v>101330</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kasimirshagen SV, Upl</t>
+          <t>Kashimirhagen SV, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655161</v>
+        <v>655141</v>
       </c>
       <c r="R10" t="n">
-        <v>6647736</v>
+        <v>6647761</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1618,22 +1590,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132124654</v>
+        <v>132976048</v>
       </c>
       <c r="B11" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,17 +1663,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kasimirshagen SV, Upl</t>
+          <t>Kashimirhagen SV, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655254</v>
+        <v>655130</v>
       </c>
       <c r="R11" t="n">
-        <v>6647727</v>
+        <v>6647775</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1725,22 +1697,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,57 +1739,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132124649</v>
+        <v>131451614</v>
       </c>
       <c r="B12" t="n">
-        <v>99122</v>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kasimirshagen SV, Upl</t>
+          <t>Tomta, Tomta, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655171</v>
+        <v>655081</v>
       </c>
       <c r="R12" t="n">
-        <v>6647768</v>
+        <v>6647893</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1841,22 +1804,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132125217</v>
+        <v>132124624</v>
       </c>
       <c r="B13" t="n">
-        <v>58115</v>
+        <v>92406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,46 +1857,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655073</v>
+        <v>655077</v>
       </c>
       <c r="R13" t="n">
-        <v>6647799</v>
+        <v>6647871</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1965,7 +1916,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1975,12 +1926,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Sång</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,32 +1953,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132124656</v>
+        <v>132124651</v>
       </c>
       <c r="B14" t="n">
-        <v>4781</v>
+        <v>92406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2042,13 +1988,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655254</v>
+        <v>655144</v>
       </c>
       <c r="R14" t="n">
-        <v>6647688</v>
+        <v>6647765</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,7 +2023,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2087,7 +2033,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,48 +2060,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132124633</v>
+        <v>131452092</v>
       </c>
       <c r="B15" t="n">
-        <v>5179</v>
+        <v>83312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>1467</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kasimirshagen SV, Upl</t>
+          <t>Svartmuttern, Svartmuttern, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655113</v>
+        <v>655143</v>
       </c>
       <c r="R15" t="n">
-        <v>6647802</v>
+        <v>6647627</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2179,22 +2125,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,48 +2167,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132124670</v>
+        <v>132976029</v>
       </c>
       <c r="B16" t="n">
-        <v>57951</v>
+        <v>96514</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2666</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kasimirshagen SV, Upl</t>
+          <t>Kashimirhagen SV, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655140</v>
+        <v>655055</v>
       </c>
       <c r="R16" t="n">
-        <v>6647863</v>
+        <v>6647789</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2286,22 +2232,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132124629</v>
+        <v>132124643</v>
       </c>
       <c r="B17" t="n">
-        <v>4781</v>
+        <v>96410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2339,21 +2285,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102306</v>
+        <v>2812</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2363,13 +2309,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655110</v>
+        <v>655149</v>
       </c>
       <c r="R17" t="n">
-        <v>6647839</v>
+        <v>6647732</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,7 +2344,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2408,12 +2354,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132124642</v>
+        <v>132976036</v>
       </c>
       <c r="B18" t="n">
-        <v>101330</v>
+        <v>96410</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,37 +2392,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kasimirshagen SV, Upl</t>
+          <t>Kashimirhagen SV, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655151</v>
+        <v>655172</v>
       </c>
       <c r="R18" t="n">
-        <v>6647732</v>
+        <v>6647727</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2505,22 +2446,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,57 +2488,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132124658</v>
+        <v>132976041</v>
       </c>
       <c r="B19" t="n">
-        <v>99122</v>
+        <v>96410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kasimirshagen SV, Upl</t>
+          <t>Kashimirhagen SV, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655194</v>
+        <v>655159</v>
       </c>
       <c r="R19" t="n">
-        <v>6647705</v>
+        <v>6647736</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2621,22 +2553,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132124632</v>
+        <v>132124622</v>
       </c>
       <c r="B20" t="n">
-        <v>5199</v>
+        <v>92199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,21 +2606,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2698,13 +2630,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655113</v>
+        <v>655081</v>
       </c>
       <c r="R20" t="n">
-        <v>6647802</v>
+        <v>6647840</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2733,7 +2665,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2743,7 +2675,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,48 +2702,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132124651</v>
+        <v>131449391</v>
       </c>
       <c r="B21" t="n">
-        <v>92373</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kasimirshagen SV, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655144</v>
+        <v>655145</v>
       </c>
       <c r="R21" t="n">
-        <v>6647765</v>
+        <v>6647787</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2835,22 +2767,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,10 +2809,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132124627</v>
+        <v>131451694</v>
       </c>
       <c r="B22" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2888,37 +2820,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kasimirshagen SV, Upl</t>
+          <t>Tomta, Tomta, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655100</v>
+        <v>655117</v>
       </c>
       <c r="R22" t="n">
-        <v>6647866</v>
+        <v>6647895</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2942,27 +2874,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,32 +2916,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132124668</v>
+        <v>132124623</v>
       </c>
       <c r="B23" t="n">
-        <v>58115</v>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,13 +2951,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655165</v>
+        <v>655079</v>
       </c>
       <c r="R23" t="n">
-        <v>6647826</v>
+        <v>6647866</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3059,7 +2986,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3069,12 +2996,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Lockläte</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3101,32 +3028,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132124624</v>
+        <v>132124670</v>
       </c>
       <c r="B24" t="n">
-        <v>92373</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3136,10 +3063,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655077</v>
+        <v>655140</v>
       </c>
       <c r="R24" t="n">
-        <v>6647871</v>
+        <v>6647863</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3171,7 +3098,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3181,7 +3108,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3208,14 +3135,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132124623</v>
+        <v>132124671</v>
       </c>
       <c r="B25" t="n">
-        <v>57951</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3243,13 +3170,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655079</v>
+        <v>655115</v>
       </c>
       <c r="R25" t="n">
-        <v>6647866</v>
+        <v>6647918</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3278,7 +3205,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3288,12 +3215,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3320,32 +3242,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132124667</v>
+        <v>132124633</v>
       </c>
       <c r="B26" t="n">
-        <v>91913</v>
+        <v>5181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3355,13 +3277,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655176</v>
+        <v>655113</v>
       </c>
       <c r="R26" t="n">
-        <v>6647822</v>
+        <v>6647802</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3390,7 +3312,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3400,7 +3322,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3427,10 +3349,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132124662</v>
+        <v>132124647</v>
       </c>
       <c r="B27" t="n">
-        <v>4781</v>
+        <v>5181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3438,42 +3360,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655225</v>
+        <v>655159</v>
       </c>
       <c r="R27" t="n">
-        <v>6647751</v>
+        <v>6647754</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3502,7 +3419,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3512,12 +3429,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3526,7 +3438,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3545,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132124639</v>
+        <v>132976049</v>
       </c>
       <c r="B28" t="n">
-        <v>4781</v>
+        <v>5181</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,37 +3467,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kasimirshagen SV, Upl</t>
+          <t>Kashimirhagen SV, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655066</v>
+        <v>655097</v>
       </c>
       <c r="R28" t="n">
-        <v>6647791</v>
+        <v>6647771</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3610,27 +3521,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På äkdre levande gran</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3657,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132124663</v>
+        <v>132124627</v>
       </c>
       <c r="B29" t="n">
-        <v>101330</v>
+        <v>4782</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3668,21 +3574,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3692,10 +3598,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655208</v>
+        <v>655100</v>
       </c>
       <c r="R29" t="n">
-        <v>6647749</v>
+        <v>6647866</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3727,7 +3633,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3737,7 +3643,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3764,10 +3675,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132124622</v>
+        <v>132124629</v>
       </c>
       <c r="B30" t="n">
-        <v>92636</v>
+        <v>4782</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3775,21 +3686,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>102306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3799,13 +3710,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655081</v>
+        <v>655110</v>
       </c>
       <c r="R30" t="n">
-        <v>6647840</v>
+        <v>6647839</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3834,7 +3745,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3844,7 +3755,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3874,7 +3790,7 @@
         <v>132124631</v>
       </c>
       <c r="B31" t="n">
-        <v>4781</v>
+        <v>4782</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3983,57 +3899,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132124661</v>
+        <v>132124639</v>
       </c>
       <c r="B32" t="n">
-        <v>99122</v>
+        <v>4782</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655238</v>
+        <v>655066</v>
       </c>
       <c r="R32" t="n">
-        <v>6647732</v>
+        <v>6647791</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4062,7 +3969,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4072,7 +3979,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På äkdre levande gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4099,10 +4011,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132124647</v>
+        <v>132124656</v>
       </c>
       <c r="B33" t="n">
-        <v>5179</v>
+        <v>4782</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4110,21 +4022,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4134,10 +4046,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>655159</v>
+        <v>655254</v>
       </c>
       <c r="R33" t="n">
-        <v>6647754</v>
+        <v>6647688</v>
       </c>
       <c r="S33" t="n">
         <v>6</v>
@@ -4169,7 +4081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4179,7 +4091,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4206,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132976049</v>
+        <v>132124662</v>
       </c>
       <c r="B34" t="n">
-        <v>5179</v>
+        <v>4782</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4217,37 +4129,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kashimirhagen SV, Upl</t>
+          <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655097</v>
+        <v>655225</v>
       </c>
       <c r="R34" t="n">
-        <v>6647771</v>
+        <v>6647751</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4271,22 +4188,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4295,6 +4217,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4313,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132976047</v>
+        <v>132976030</v>
       </c>
       <c r="B35" t="n">
-        <v>101348</v>
+        <v>4782</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4324,21 +4247,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4348,10 +4271,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655153</v>
+        <v>655073</v>
       </c>
       <c r="R35" t="n">
-        <v>6647721</v>
+        <v>6647783</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4383,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4393,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4420,48 +4343,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132976040</v>
+        <v>132124668</v>
       </c>
       <c r="B36" t="n">
-        <v>101348</v>
+        <v>58136</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kashimirhagen SV, Upl</t>
+          <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655159</v>
+        <v>655165</v>
       </c>
       <c r="R36" t="n">
-        <v>6647736</v>
+        <v>6647826</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4485,22 +4408,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4527,10 +4455,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132976043</v>
+        <v>132125217</v>
       </c>
       <c r="B37" t="n">
-        <v>91928</v>
+        <v>58136</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4538,37 +4466,49 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kashimirhagen SV, Upl</t>
+          <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655141</v>
+        <v>655073</v>
       </c>
       <c r="R37" t="n">
-        <v>6647761</v>
+        <v>6647799</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4592,22 +4532,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4634,10 +4579,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132976044</v>
+        <v>131450235</v>
       </c>
       <c r="B38" t="n">
-        <v>101348</v>
+        <v>5199</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4645,37 +4590,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kashimirhagen SV, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655143</v>
+        <v>655056</v>
       </c>
       <c r="R38" t="n">
-        <v>6647734</v>
+        <v>6647808</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4699,22 +4644,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4741,10 +4686,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132976038</v>
+        <v>132124632</v>
       </c>
       <c r="B39" t="n">
-        <v>101348</v>
+        <v>5201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,37 +4697,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kashimirhagen SV, Upl</t>
+          <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655167</v>
+        <v>655113</v>
       </c>
       <c r="R39" t="n">
-        <v>6647731</v>
+        <v>6647802</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4806,22 +4751,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4848,48 +4793,60 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132976033</v>
+        <v>131448147</v>
       </c>
       <c r="B40" t="n">
-        <v>91928</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kashimirhagen SV, Upl</t>
+          <t>Stamsäng, Stamsäng, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655131</v>
+        <v>655291</v>
       </c>
       <c r="R40" t="n">
-        <v>6647804</v>
+        <v>6647717</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4913,22 +4870,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4937,6 +4894,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4955,48 +4913,57 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132976048</v>
+        <v>131448213</v>
       </c>
       <c r="B41" t="n">
-        <v>91928</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kashimirhagen SV, Upl</t>
+          <t>Stamsäng, Stamsäng, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655130</v>
+        <v>655284</v>
       </c>
       <c r="R41" t="n">
-        <v>6647775</v>
+        <v>6647716</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5020,22 +4987,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5062,48 +5029,57 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132976035</v>
+        <v>132124649</v>
       </c>
       <c r="B42" t="n">
-        <v>101348</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kashimirhagen SV, Upl</t>
+          <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655173</v>
+        <v>655171</v>
       </c>
       <c r="R42" t="n">
-        <v>6647726</v>
+        <v>6647768</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5127,22 +5103,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5169,48 +5145,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132976030</v>
+        <v>132124653</v>
       </c>
       <c r="B43" t="n">
-        <v>4781</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kashimirhagen SV, Upl</t>
+          <t>Kasimirshagen SV, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655073</v>
+        <v>655286</v>
       </c>
       <c r="R43" t="n">
-        <v>6647783</v>
+        <v>6647730</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5234,22 +5219,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5273,6 +5258,1201 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132124658</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kasimirshagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>655194</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6647705</v>
+      </c>
+      <c r="S44" t="n">
+        <v>12</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132124661</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kasimirshagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>655238</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6647732</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132124642</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kasimirshagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>655151</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6647732</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132124646</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kasimirshagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>655161</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6647736</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132124663</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kasimirshagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>655208</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6647749</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132976035</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>655173</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6647726</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132976038</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>655167</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6647731</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132976040</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>655159</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6647736</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132976044</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>655143</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6647734</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132976047</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>655153</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6647721</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132976042</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kashimirhagen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>655159</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6647735</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
